--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
   <si>
     <t>Filename</t>
   </si>
@@ -808,667 +808,676 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9963,0.0005,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9926,0.0004,0.0001,0.0023</t>
-  </si>
-  <si>
-    <t>0.0143,0.0027,0.0012,0.9925</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9848,0.0015,0.0062,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.0000,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.9757,0.0004,0.0004,0.0167</t>
+  </si>
+  <si>
+    <t>0.0472,0.0011,0.0002,0.9812</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0006,0.0000,0.0000</t>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5257,0.0001,0.5914,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0524,0.0003,0.9649,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.9540,0.0014,0.0378,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.9956,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9981,0.0015,0.0000</t>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0150,0.0002,0.9860,0.0001</t>
+  </si>
+  <si>
+    <t>0.6214,0.0001,0.5715,0.0000</t>
+  </si>
+  <si>
+    <t>0.8097,0.0003,0.3219,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.0007,0.9909,0.0002</t>
+  </si>
+  <si>
+    <t>0.1953,0.0004,0.8609,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0684,0.9629,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9981,0.0006,0.0001</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.8299,0.0006,0.1749,0.0003</t>
-  </si>
-  <si>
-    <t>0.2642,0.0015,0.7123,0.0011</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0090,0.0002,0.9899,0.0002</t>
-  </si>
-  <si>
-    <t>0.1229,0.0000,0.9421,0.0000</t>
-  </si>
-  <si>
-    <t>0.2647,0.0001,0.8378,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0005,0.9954,0.0006</t>
-  </si>
-  <si>
-    <t>0.0312,0.9835,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.6595,0.2270,0.0236,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9997,0.0025</t>
-  </si>
-  <si>
-    <t>0.0014,0.9973,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9903,0.0000,0.0162,0.0000</t>
-  </si>
-  <si>
-    <t>0.1046,0.0004,0.9331,0.0003</t>
-  </si>
-  <si>
-    <t>0.2576,0.7777,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9985,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.8745,0.0939,0.0039</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9974,0.0006</t>
-  </si>
-  <si>
-    <t>0.0285,0.0544,0.9107,0.0019</t>
-  </si>
-  <si>
-    <t>0.0045,0.0000,0.9934,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0055,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0044,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0398,0.2041,0.0009,0.8274</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0505,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0071,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9991,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0088,0.9968,0.0008</t>
-  </si>
-  <si>
-    <t>0.9955,0.0062,0.0003,0.0000</t>
+    <t>0.9905,0.0001,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0465,0.0031,0.9342,0.0013</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0193,0.0003,0.9768,0.0010</t>
+  </si>
+  <si>
+    <t>0.0526,0.0000,0.9753,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0000,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0013</t>
+  </si>
+  <si>
+    <t>0.0984,0.9425,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.5404,0.3175,0.0248,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0028,0.9986,0.0055</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9786,0.0003,0.0238,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0805,0.9298,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.9800,0.0523,0.0002</t>
+  </si>
+  <si>
+    <t>0.1219,0.1506,0.1757,0.0030</t>
+  </si>
+  <si>
+    <t>0.0087,0.0001,0.9804,0.0012</t>
+  </si>
+  <si>
+    <t>0.0076,0.0083,0.9771,0.0024</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9959,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.0118,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.6333,0.0037,0.0005,0.3237</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1300,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0034,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.0001,0.9953,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0034,0.9971,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0029,0.9998,0.0034</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9765,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0083,0.9989,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.9990,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9908,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0206,0.9880,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0627,0.0009,0.9540,0.0003</t>
+  </si>
+  <si>
+    <t>0.0793,0.0088,0.8842,0.0004</t>
+  </si>
+  <si>
+    <t>0.0023,0.0005,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9640,0.9724,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.5243,0.9548,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.0205,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0020,0.9994</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0047,0.0005,0.0008,0.9968</t>
+  </si>
+  <si>
+    <t>0.0032,0.0000,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9984,0.0586,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9705,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3060,0.9951,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.9452,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9930,0.9825,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9859,0.0258,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0076,0.0033,0.9903,0.0002</t>
+  </si>
+  <si>
+    <t>0.7410,0.0000,0.3707,0.0002</t>
+  </si>
+  <si>
+    <t>0.0061,0.0002,0.9955,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0508,0.9523,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.9955,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.8465,0.2485,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.2912,0.0077,0.6299,0.0003</t>
+  </si>
+  <si>
+    <t>0.6953,0.0002,0.3582,0.0002</t>
+  </si>
+  <si>
+    <t>0.7250,0.0717,0.0403,0.0020</t>
+  </si>
+  <si>
+    <t>0.5589,0.0278,0.1012,0.0082</t>
+  </si>
+  <si>
+    <t>0.0002,0.0025,0.0009,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0059,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9933,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9176,0.1003,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.9140,0.0775,0.0064,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.7788,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.1055,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.0016,0.9871,0.0002</t>
+  </si>
+  <si>
+    <t>0.0339,0.0043,0.9474,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0366,0.0003,0.9652,0.0001</t>
+  </si>
+  <si>
+    <t>0.2590,0.0000,0.8726,0.0000</t>
+  </si>
+  <si>
+    <t>0.0049,0.0001,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.0001,0.0004,0.9969</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.9855,0.9840,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9958,0.0008,0.0014</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0009,0.9994,0.0031</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9463,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0022,0.9976,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9993,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9993,0.0000</t>
+    <t>0.0849,0.9174,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.9832,0.0001,0.0012,0.0107</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9984,0.0058</t>
+  </si>
+  <si>
+    <t>0.9324,0.0000,0.0868,0.0003</t>
+  </si>
+  <si>
+    <t>0.4282,0.5579,0.0101,0.0009</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9913,0.0032,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.6218,0.1342,0.0445,0.0001</t>
+  </si>
+  <si>
+    <t>0.9730,0.0042,0.0137,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0025,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0025,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.8569,0.1405,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.9946,0.0056,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.3550,0.0070,0.6527,0.0006</t>
+  </si>
+  <si>
+    <t>0.9925,0.0146,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9905,0.0035,0.0037,0.0028</t>
+  </si>
+  <si>
+    <t>0.9896,0.0090,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9224,0.0271,0.0254,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0349,0.9979,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9996,0.0012</t>
+  </si>
+  <si>
+    <t>0.0004,0.0009,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0068,0.0002,0.9916,0.0002</t>
+  </si>
+  <si>
+    <t>0.0138,0.0056,0.9731,0.0004</t>
+  </si>
+  <si>
+    <t>0.0083,0.0124,0.9859,0.0001</t>
+  </si>
+  <si>
+    <t>0.0147,0.0217,0.9509,0.0001</t>
+  </si>
+  <si>
+    <t>0.5196,0.0018,0.4994,0.0000</t>
+  </si>
+  <si>
+    <t>0.9550,0.0005,0.0396,0.0002</t>
+  </si>
+  <si>
+    <t>0.0558,0.0006,0.9590,0.0001</t>
+  </si>
+  <si>
+    <t>0.4676,0.7228,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0188,0.9883,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9458,0.1026,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.3864,0.7531,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.4917,0.7320,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8179,0.0756,0.0196,0.0007</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0011,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0225,0.0103,0.9563,0.0011</t>
+  </si>
+  <si>
+    <t>0.0025,0.0040,0.9921,0.0031</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9984,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.0020,0.9966,0.0015</t>
+  </si>
+  <si>
+    <t>0.0078,0.0631,0.9734,0.0012</t>
+  </si>
+  <si>
+    <t>0.0003,0.0022,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0059,0.9932,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9998,0.0010</t>
+  </si>
+  <si>
+    <t>0.0306,0.0097,0.9521,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0002,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0244,0.0000,0.9850,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0007,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0178,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0068,0.0008,0.9894,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0011,0.9983,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.0729,0.0006,0.9468,0.0005</t>
-  </si>
-  <si>
-    <t>0.1961,0.0083,0.7082,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0010,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9434,0.9870,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3373,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0144,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9952,0.3871,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0000,0.0010,0.9973</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0388,0.0000,0.0000,0.9927</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.0012,0.9976</t>
-  </si>
-  <si>
-    <t>0.0026,0.0000,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9929,0.5880,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9952,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9627,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3260,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9877,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9923,0.5637,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.0057,0.9863,0.0011</t>
+  </si>
+  <si>
+    <t>0.9034,0.0008,0.0448,0.0037</t>
+  </si>
+  <si>
+    <t>0.9714,0.0005,0.0127,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0001,0.0013,0.0003</t>
   </si>
   <si>
     <t>0.9996,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0039,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0022</t>
-  </si>
-  <si>
-    <t>0.1187,0.0019,0.8984,0.0001</t>
-  </si>
-  <si>
-    <t>0.9871,0.0000,0.0112,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9991,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.9949,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.8975,0.1798,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.1469,0.0006,0.8593,0.0008</t>
-  </si>
-  <si>
-    <t>0.6970,0.0003,0.3481,0.0002</t>
-  </si>
-  <si>
-    <t>0.3461,0.1023,0.1225,0.0046</t>
-  </si>
-  <si>
-    <t>0.0936,0.0088,0.7790,0.0037</t>
-  </si>
-  <si>
-    <t>0.0003,0.0717,0.0003,0.9956</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9920,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9866,0.0169,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.3048,0.7150,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.9756,0.0341,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.2593,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0243,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.0017,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.9926,0.0001,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.3578,0.0001,0.7231,0.0001</t>
-  </si>
-  <si>
-    <t>0.5259,0.0001,0.5327,0.0003</t>
-  </si>
-  <si>
-    <t>0.1698,0.0001,0.8761,0.0001</t>
-  </si>
-  <si>
-    <t>0.0292,0.0001,0.0013,0.9839</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.7763,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0670,0.9465,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9586,0.0000,0.0165,0.0059</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9979,0.0018</t>
-  </si>
-  <si>
-    <t>0.9869,0.0000,0.0175,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7724,0.2997,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0865,0.0371,0.7428,0.0002</t>
-  </si>
-  <si>
-    <t>0.9497,0.0274,0.0049,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0001,0.0000</t>
+    <t>0.9987,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0017,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0001,0.0001</t>
+    <t>0.9991,0.0010,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0010,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.7784,0.2587,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9920,0.0125,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0334,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0041,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9966,0.0030,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0030,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0095,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0099,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.0022,0.9826,0.0009</t>
-  </si>
-  <si>
-    <t>0.0024,0.0002,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.0454,0.0116,0.9188,0.0009</t>
-  </si>
-  <si>
-    <t>0.0477,0.0357,0.8932,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0597,0.9821,0.0000</t>
-  </si>
-  <si>
-    <t>0.0715,0.0010,0.9299,0.0001</t>
-  </si>
-  <si>
-    <t>0.9560,0.0011,0.0352,0.0001</t>
-  </si>
-  <si>
-    <t>0.0356,0.0008,0.9672,0.0003</t>
-  </si>
-  <si>
-    <t>0.0519,0.9746,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0574,0.9726,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9662,0.0751,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9212,0.1096,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0288,0.9789,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9716,0.0047,0.0049,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0000,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0004,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0431,0.0019,0.9498,0.0009</t>
-  </si>
-  <si>
-    <t>0.0606,0.0015,0.9333,0.0029</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9993,0.0030</t>
-  </si>
-  <si>
-    <t>0.0013,0.0042,0.9939,0.0017</t>
-  </si>
-  <si>
-    <t>0.0092,0.2179,0.9575,0.0011</t>
-  </si>
-  <si>
-    <t>0.0035,0.0016,0.9925,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.0030,0.9961,0.0005</t>
-  </si>
-  <si>
-    <t>0.9980,0.0011,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0024,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0020,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0067,0.0183,0.9766,0.0015</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.1182,0.0000,0.9527,0.0000</t>
-  </si>
-  <si>
-    <t>0.0076,0.0059,0.9883,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0523,0.9895,0.0014</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0007,0.9942,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0039,0.9905,0.0024</t>
-  </si>
-  <si>
-    <t>0.9883,0.0004,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.9471,0.0001,0.0610,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0011,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.0055,0.9901,0.0008</t>
-  </si>
-  <si>
-    <t>0.4605,0.0003,0.6236,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9981,0.0051</t>
-  </si>
-  <si>
-    <t>0.0047,0.0006,0.9911,0.0005</t>
-  </si>
-  <si>
-    <t>0.0027,0.0008,0.9910,0.0049</t>
-  </si>
-  <si>
-    <t>0.9926,0.0000,0.0002,0.0034</t>
-  </si>
-  <si>
-    <t>0.0019,0.0011,0.0002,0.9985</t>
-  </si>
-  <si>
-    <t>0.2436,0.0003,0.0022,0.8217</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9939,0.0001,0.0003,0.0015</t>
+    <t>0.0001,0.0022,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0041,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0009,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.1363,0.0000,0.9026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0006,0.9926,0.0191</t>
+  </si>
+  <si>
+    <t>0.0026,0.0004,0.9941,0.0009</t>
+  </si>
+  <si>
+    <t>0.0500,0.0324,0.7657,0.0135</t>
+  </si>
+  <si>
+    <t>0.9665,0.0001,0.0020,0.0127</t>
+  </si>
+  <si>
+    <t>0.0002,0.0088,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.1346,0.0000,0.0003,0.9293</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0000,0.0005</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1863,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1868,7 +1877,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1882,7 +1891,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1896,7 +1905,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1910,7 +1919,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1924,7 +1933,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1938,7 +1947,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1952,7 +1961,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1966,7 +1975,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1980,7 +1989,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1994,7 +2003,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2008,7 +2017,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2022,7 +2031,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2033,10 +2042,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2047,10 +2056,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2064,7 +2073,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2075,10 +2084,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2092,7 +2101,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2106,7 +2115,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2120,7 +2129,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2134,7 +2143,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2148,7 +2157,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2162,7 +2171,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,7 +2185,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2190,7 +2199,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2204,7 +2213,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2218,7 +2227,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2229,10 +2238,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2246,7 +2255,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2260,7 +2269,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,7 +2283,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2288,7 +2297,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2302,7 +2311,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2316,7 +2325,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2327,10 +2336,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2344,7 +2353,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2358,7 +2367,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2369,10 +2378,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2386,7 +2395,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2400,7 +2409,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2414,7 +2423,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2428,7 +2437,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2442,7 +2451,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2456,7 +2465,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2467,10 +2476,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2484,7 +2493,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2498,7 +2507,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2512,7 +2521,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2526,7 +2535,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2540,7 +2549,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2554,7 +2563,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2568,7 +2577,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2582,7 +2591,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2596,7 +2605,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2610,7 +2619,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2624,7 +2633,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2638,7 +2647,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2652,7 +2661,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2666,7 +2675,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2680,7 +2689,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2694,7 +2703,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2792,7 +2801,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2806,7 +2815,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2820,7 +2829,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2834,7 +2843,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2848,7 +2857,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2859,10 +2868,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2876,7 +2885,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2890,7 +2899,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2904,7 +2913,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2918,7 +2927,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2932,7 +2941,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2946,7 +2955,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2960,7 +2969,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2974,7 +2983,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2985,10 +2994,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3002,7 +3011,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3016,7 +3025,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3030,7 +3039,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3044,7 +3053,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,7 +3067,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3072,7 +3081,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3086,7 +3095,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3100,7 +3109,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3114,7 +3123,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3128,7 +3137,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3142,7 +3151,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3156,7 +3165,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3170,7 +3179,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3184,7 +3193,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3198,7 +3207,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3212,7 +3221,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3226,7 +3235,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3240,7 +3249,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3254,7 +3263,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3268,7 +3277,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3282,7 +3291,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3296,7 +3305,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3310,7 +3319,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3324,7 +3333,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3338,7 +3347,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3352,7 +3361,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3366,7 +3375,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3380,7 +3389,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3394,7 +3403,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3408,7 +3417,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3422,7 +3431,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3436,7 +3445,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3450,7 +3459,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3464,7 +3473,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3478,7 +3487,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3489,10 +3498,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3506,7 +3515,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3520,7 +3529,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3534,7 +3543,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3548,7 +3557,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3562,7 +3571,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3576,7 +3585,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,7 +3599,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3601,10 +3610,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3618,7 +3627,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3632,7 +3641,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3646,7 +3655,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3660,7 +3669,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3674,7 +3683,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3688,7 +3697,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3702,7 +3711,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3716,7 +3725,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3727,10 +3736,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3744,7 +3753,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3758,7 +3767,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3772,7 +3781,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3786,7 +3795,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3800,7 +3809,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3814,7 +3823,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3828,7 +3837,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3842,7 +3851,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3856,7 +3865,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>335</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3870,7 +3879,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3884,7 +3893,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,7 +3907,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3912,7 +3921,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>272</v>
+        <v>393</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3926,7 +3935,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3940,7 +3949,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3954,7 +3963,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3968,7 +3977,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3982,7 +3991,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3996,7 +4005,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4010,7 +4019,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4024,7 +4033,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4038,7 +4047,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>397</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4049,10 +4058,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4066,7 +4075,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4080,7 +4089,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4091,10 +4100,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4108,7 +4117,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4122,7 +4131,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4136,7 +4145,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>347</v>
+        <v>406</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4150,7 +4159,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4164,7 +4173,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>404</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4178,7 +4187,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4192,7 +4201,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4206,7 +4215,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>406</v>
+        <v>318</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4220,7 +4229,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4234,7 +4243,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4248,7 +4257,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4262,7 +4271,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4276,7 +4285,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4290,7 +4299,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4304,7 +4313,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>271</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4318,7 +4327,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4332,7 +4341,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>319</v>
+        <v>395</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4346,7 +4355,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4360,7 +4369,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4374,7 +4383,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4388,7 +4397,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4402,7 +4411,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4416,7 +4425,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4430,7 +4439,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4444,7 +4453,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4458,7 +4467,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4472,7 +4481,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4486,7 +4495,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4500,7 +4509,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4514,7 +4523,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,7 +4537,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4542,7 +4551,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4553,10 +4562,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4570,7 +4579,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4584,7 +4593,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4598,7 +4607,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4612,7 +4621,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4626,7 +4635,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4637,10 +4646,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4654,7 +4663,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4668,7 +4677,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4682,7 +4691,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4696,7 +4705,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4710,7 +4719,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4724,7 +4733,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4738,7 +4747,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4752,7 +4761,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4766,7 +4775,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4780,7 +4789,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4794,7 +4803,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4808,7 +4817,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4822,7 +4831,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4836,7 +4845,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4850,7 +4859,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4864,7 +4873,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4878,7 +4887,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>451</v>
+        <v>347</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4892,7 +4901,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>452</v>
+        <v>271</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4906,7 +4915,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4920,7 +4929,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4934,7 +4943,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4948,7 +4957,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4962,7 +4971,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4976,7 +4985,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4990,7 +4999,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5004,7 +5013,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5018,7 +5027,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5032,7 +5041,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5046,7 +5055,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5060,7 +5069,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5074,7 +5083,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5088,7 +5097,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5102,7 +5111,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5116,7 +5125,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>348</v>
+        <v>468</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5130,7 +5139,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>320</v>
+        <v>469</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5144,7 +5153,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5158,7 +5167,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5172,7 +5181,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5186,7 +5195,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5200,7 +5209,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5214,7 +5223,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5228,7 +5237,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5242,7 +5251,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5256,7 +5265,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5270,7 +5279,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5284,7 +5293,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5298,7 +5307,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5312,7 +5321,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5326,7 +5335,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5340,7 +5349,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5354,7 +5363,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5368,7 +5377,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5382,7 +5391,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5396,7 +5405,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5410,7 +5419,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
